--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Proceso integrado con cierre, fiscalidad, reporting y controles automáticos, con revisión periódica de criterios y excepciones.</t>
   </si>
   <si>
-    <t>Modelo AI-enabled que detecta tratamientos anómalos, sugiere clasificaciones contable-fiscales y explica variaciones de resultados financieros.</t>
-  </si>
-  <si>
-    <t>Accurate tax report generation; Identify inconsistencies in master data records; Generate account variance analysis and intelligent explanations</t>
+    <t>Modelo basado en IA que detecta tratamientos anómalos, sugiere clasificaciones contable-fiscales y explica variaciones de resultados financieros.</t>
+  </si>
+  <si>
+    <t>Generación precisa de informes fiscales; Identificación de inconsistencias en los registros de datos maestros; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Existen políticas contable-fiscales para operaciones de tesorería?
@@ -167,10 +167,10 @@
     <t>Devengos integrados con contratos, bancos, deuda, cierre y reporting, con controles automáticos y explicación de variaciones.</t>
   </si>
   <si>
-    <t>AI identifica devengos esperados, detecta omisiones o anomalías y genera explicaciones inteligentes de variaciones financieras.</t>
-  </si>
-  <si>
-    <t>Identify missing monthly accruals based on historic trends; Generate account variance analysis and intelligent explanations; Reconcile account balances at transaction level</t>
+    <t>IA identifica devengos esperados, detecta omisiones o anomalías y genera explicaciones inteligentes de variaciones financieras.</t>
+  </si>
+  <si>
+    <t>Identificación de provisiones mensuales omitidas a partir de tendencias históricas; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; Conciliación de saldos contables a nivel de transacción</t>
   </si>
   <si>
     <t>¿Se registran devengos de forma sistemática?
@@ -203,10 +203,10 @@
     <t>Gobierno integrado con bancos, ERP, TMS, pagos, deuda y reporting, con controles automáticos y gestión de incidencias.</t>
   </si>
   <si>
-    <t>AI detecta inconsistencias en datos maestros, propone remediación y guía workflows adaptativos de cambios financieros/bancarios.</t>
-  </si>
-  <si>
-    <t>Identify inconsistencies in master data records; Guided adaptable workflows for master data record changes; Generate metadata documentation</t>
+    <t>IA detecta inconsistencias en datos maestros, propone remediación y guía workflows adaptativos de cambios financieros/bancarios.</t>
+  </si>
+  <si>
+    <t>Identificación de inconsistencias en los registros de datos maestros; Flujos guiados y adaptables para cambios en datos maestros; Generación de documentación de metadatos</t>
   </si>
   <si>
     <t>¿Existen owners de datos maestros bancarios?
@@ -239,10 +239,10 @@
     <t>Reporting integrado con deuda, liquidez, inversiones, riesgos financieros, forecast y acciones de gestión.</t>
   </si>
   <si>
-    <t>Reporting AI-enabled con narrativa automática, explicación de drivers, alertas tempranas y recomendaciones sobre coste financiero y liquidez.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; Generate account variance analysis and intelligent explanations; FinanceAI Insights Platform</t>
+    <t>Reporting basado en IA con narrativa automática, explicación de drivers, alertas tempranas y recomendaciones sobre coste financiero y liquidez.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; FinanceAI Insights Platform</t>
   </si>
   <si>
     <t>¿Se reportan resultados financieros de tesorería?
@@ -278,10 +278,10 @@
     <t>Gestión integrada con posiciones, exposiciones, coberturas, escenarios, límites y comités de seguimiento.</t>
   </si>
   <si>
-    <t>Modelo AI-enabled que monitoriza exposiciones, detecta desviaciones frente a límites y recomienda acciones de cobertura o mitigación.</t>
-  </si>
-  <si>
-    <t>Optimize foreign exchange operations by evaluating foreign exchange data and identifying patterns and trends to reduce financial risks; AI agents for credit underwriting; Predictive compliance monitoring</t>
+    <t>Modelo basado en IA que monitoriza exposiciones, detecta desviaciones frente a límites y recomienda acciones de cobertura o mitigación.</t>
+  </si>
+  <si>
+    <t>Optimización de las operaciones de divisa evaluando datos de tipo de cambio e identificando patrones y tendencias para reducir riesgos financieros; Agentes de IA para el análisis de riesgo crediticio; Monitorización predictiva del cumplimiento</t>
   </si>
   <si>
     <t>¿Existe política de riesgos financieros?
@@ -314,10 +314,10 @@
     <t>Gestión integrada de FX con forecast, operaciones, posiciones, escenarios, límites, efectividad de cobertura y contabilidad.</t>
   </si>
   <si>
-    <t>AI identifica patrones FX, anticipa exposición, simula escenarios y recomienda estrategias de cobertura según riesgo, coste y política.</t>
-  </si>
-  <si>
-    <t>Optimize foreign exchange operations by evaluating foreign exchange data and identifying patterns and trends to reduce financial risks; Predictive Analysis + GenAI; Generate investing strategies</t>
+    <t>IA identifica patrones FX, anticipa exposición, simula escenarios y recomienda estrategias de cobertura según riesgo, coste y política.</t>
+  </si>
+  <si>
+    <t>Optimización de las operaciones de divisa evaluando datos de tipo de cambio e identificando patrones y tendencias para reducir riesgos financieros; Análisis predictivo + GenAI; Generación de estrategias de inversión</t>
   </si>
   <si>
     <t>¿Se mide exposición FX por moneda y horizonte?
@@ -350,10 +350,10 @@
     <t>Gestión integrada con deuda, inversiones, bancos, derivados, límites, escenarios macro y decisiones de financiación/inversión.</t>
   </si>
   <si>
-    <t>AI calcula sensibilidades, anticipa cambios de riesgo, alerta sobre límites y recomienda acciones de refinanciación, cobertura o diversificación.</t>
-  </si>
-  <si>
-    <t>AI agents for credit underwriting; Predictive company valuation analyzing financial data; Grid and energy efficiency optimization</t>
+    <t>IA calcula sensibilidades, anticipa cambios de riesgo, alerta sobre límites y recomienda acciones de refinanciación, cobertura o diversificación.</t>
+  </si>
+  <si>
+    <t>Agentes de IA para el análisis de riesgo crediticio; Valoración predictiva de la compañía a partir del análisis de datos financieros; Optimización de la red y de la eficiencia energética</t>
   </si>
   <si>
     <t>¿Se mide sensibilidad a tipos?
@@ -386,10 +386,10 @@
     <t>Stress testing integrado con cash forecast, deuda, covenants, FX, tipos, liquidez, capital allocation y comités.</t>
   </si>
   <si>
-    <t>AI simula escenarios dinámicos, identifica early warnings, estima impactos y recomienda respuestas financieras preventivas.</t>
-  </si>
-  <si>
-    <t>Predictive cash flow forecasting tool; Optimize foreign exchange operations; Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA simula escenarios dinámicos, identifica early warnings, estima impactos y recomienda respuestas financieras preventivas.</t>
+  </si>
+  <si>
+    <t>Herramienta predictiva de previsión de flujo de caja; Optimización de las operaciones de divisa; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Se realizan stress tests financieros?
@@ -425,10 +425,10 @@
     <t>Estrategia integrada con plan estratégico, cash forecast, inversiones, mercado, riesgos financieros y capital allocation.</t>
   </si>
   <si>
-    <t>AI recomienda estrategias de financiación considerando mercado, coste de capital, rating, liquidez, escenarios y objetivos corporativos.</t>
-  </si>
-  <si>
-    <t>Generate investing strategies from consolidated market conditions, internal financial performance, and firm objectives; Predictive company valuation analyzing financial data; Generate executive level overview of company financial health</t>
+    <t>IA recomienda estrategias de financiación considerando mercado, coste de capital, rating, liquidez, escenarios y objetivos corporativos.</t>
+  </si>
+  <si>
+    <t>Generación de estrategias de inversión a partir de las condiciones de mercado consolidadas, el rendimiento financiero interno y los objetivos de la firma; Valoración predictiva de la compañía a partir del análisis de datos financieros; Generación de una visión ejecutiva de la salud financiera de la compañía</t>
   </si>
   <si>
     <t>¿Existe estrategia de financiación?
@@ -461,10 +461,10 @@
     <t>Gestión integrada en TMS/ERP con alertas, escenarios, covenant forecasting, relación bancaria y control de documentación.</t>
   </si>
   <si>
-    <t>AI anticipa riesgos de covenant, recomienda acciones de refinanciación y sintetiza documentación financiera para financiadores.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; Predictive cash flow forecasting tool; Research-based report generation / KYC</t>
+    <t>IA anticipa riesgos de covenant, recomienda acciones de refinanciación y sintetiza documentación financiera para financiadores.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Herramienta predictiva de previsión de flujo de caja; Generación de informes de investigación / KYC</t>
   </si>
   <si>
     <t>¿Se monitorizan covenants y vencimientos?
@@ -497,10 +497,10 @@
     <t>Ejecución integrada con estrategia de financiación, ventanas de mercado, rating, inversores, bancos, riesgos y reporting de operación.</t>
   </si>
   <si>
-    <t>AI analiza condiciones de mercado, simula alternativas de instrumentos y recomienda timing, estructura y fuentes óptimas de financiación.</t>
-  </si>
-  <si>
-    <t>AI agents for algorithmic trading and market simulation; Generate investing strategies; Predictive company valuation analyzing financial data</t>
+    <t>IA analiza condiciones de mercado, simula alternativas de instrumentos y recomienda timing, estructura y fuentes óptimas de financiación.</t>
+  </si>
+  <si>
+    <t>Agentes de IA para trading algorítmico y simulación de mercado; Generación de estrategias de inversión; Valoración predictiva de la compañía a partir del análisis de datos financieros</t>
   </si>
   <si>
     <t>¿Se comparan fuentes e instrumentos?
@@ -533,10 +533,10 @@
     <t>Inteligencia integrada con estrategia de financiación, deuda, inversión, riesgos, escenarios y decisiones de timing.</t>
   </si>
   <si>
-    <t>AI sintetiza señales de mercado, detecta oportunidades de financiación, genera alertas y recomienda acciones de capital markets.</t>
-  </si>
-  <si>
-    <t>Next-level market intelligence; Generate investing strategies; AI agents for algorithmic trading and market simulation</t>
+    <t>IA sintetiza señales de mercado, detecta oportunidades de financiación, genera alertas y recomienda acciones de capital markets.</t>
+  </si>
+  <si>
+    <t>Inteligencia de mercado de nueva generación; Generación de estrategias de inversión; Agentes de IA para trading algorítmico y simulación de mercado</t>
   </si>
   <si>
     <t>¿Se monitorizan mercados de deuda/capitales?
@@ -572,10 +572,10 @@
     <t>Forecast integrado con ERP/TMS, presupuesto, ventas, compras, deuda, working capital, escenarios y revisión de desviaciones.</t>
   </si>
   <si>
-    <t>Cash forecasting predictivo AI-enabled con aprendizaje histórico, señales operativas, escenarios dinámicos y recomendaciones de acción.</t>
-  </si>
-  <si>
-    <t>Predictive cash flow forecasting tool; Enhance cash flow analysis, minimizing liquidity risks, improving forecasting accuracy, and maximizing returns on cash holdings; Intraday liquidity optimization</t>
+    <t>Cash forecasting predictivo basado en IA con aprendizaje histórico, señales operativas, escenarios dinámicos y recomendaciones de acción.</t>
+  </si>
+  <si>
+    <t>Herramienta predictiva de previsión de flujo de caja; Mejora del análisis de flujo de caja, minimizando riesgos de liquidez, mejorando la precisión de las previsiones y maximizando el rendimiento de la tesorería; Optimización de la liquidez intradía</t>
   </si>
   <si>
     <t>¿Existe metodología formal de cash forecast?
@@ -608,10 +608,10 @@
     <t>Visibilidad integrada e intradía con TMS/bancos, cash pooling, límites, alertas y conciliación automatizada.</t>
   </si>
   <si>
-    <t>AI optimiza liquidez intradía, anticipa necesidades, detecta saldos ociosos/restricciones y recomienda movimientos o inversiones.</t>
-  </si>
-  <si>
-    <t>Intraday liquidity optimization; Enhance cash flow analysis, minimizing liquidity risks; Data access for all</t>
+    <t>IA optimiza liquidez intradía, anticipa necesidades, detecta saldos ociosos/restricciones y recomienda movimientos o inversiones.</t>
+  </si>
+  <si>
+    <t>Optimización de la liquidez intradía; Mejora del análisis de flujo de caja, minimizando riesgos de liquidez; Acceso a datos para toda la organización</t>
   </si>
   <si>
     <t>¿Existe visibilidad diaria/intradía de caja?
@@ -644,10 +644,10 @@
     <t>Gestión integrada de liquidez con O2C/P2P, forecast, deuda, inversiones, pagos, cobros, DSO/DPO/DIO y escenarios.</t>
   </si>
   <si>
-    <t>AI recomienda términos de pago/cobro, timing óptimo, acciones sobre working capital e inversiones de excedentes según liquidez y riesgo.</t>
-  </si>
-  <si>
-    <t>Recommend optimal payment terms to improve DSO; Recommend most optimal payment timing; Dynamic inventory management</t>
+    <t>IA recomienda términos de pago/cobro, timing óptimo, acciones sobre working capital e inversiones de excedentes según liquidez y riesgo.</t>
+  </si>
+  <si>
+    <t>Recomendación de condiciones de pago óptimas para mejorar el DSO; Recomendación del momento óptimo de pago; Gestión dinámica de inventario</t>
   </si>
   <si>
     <t>¿Se conectan liquidez y working capital?
@@ -680,10 +680,10 @@
     <t>Rutinas integradas de liquidez con comité, decisiones, seguimiento de acciones, alertas, escenarios y beneficios esperados.</t>
   </si>
   <si>
-    <t>Reporting AI-enabled con narrativa ejecutiva, alertas, explicación de desviaciones, escenarios y recomendaciones de liquidez.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; FinanceAI Insights Platform; Generate account variance analysis and intelligent explanations</t>
+    <t>Reporting basado en IA con narrativa ejecutiva, alertas, explicación de desviaciones, escenarios y recomendaciones de liquidez.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
     <t>¿Existe pack de tesorería?
@@ -719,10 +719,10 @@
     <t>Gobierno integrado con cash forecast, riesgos financieros, límites de contraparte, escenarios, compliance y revisión periódica de performance.</t>
   </si>
   <si>
-    <t>AI recomienda asignación de excedentes considerando liquidez futura, retorno, riesgo, límites, mercado y restricciones corporativas.</t>
-  </si>
-  <si>
-    <t>Enhance cash flow analysis, minimizing liquidity risks, improving forecasting accuracy, and maximizing returns on cash holdings; Generate investing strategies; Predictive cash flow forecasting tool</t>
+    <t>IA recomienda asignación de excedentes considerando liquidez futura, retorno, riesgo, límites, mercado y restricciones corporativas.</t>
+  </si>
+  <si>
+    <t>Mejora del análisis de flujo de caja, minimizando riesgos de liquidez, mejorando la precisión de las previsiones y maximizando el rendimiento de la tesorería; Generación de estrategias de inversión; Herramienta predictiva de previsión de flujo de caja</t>
   </si>
   <si>
     <t>¿Existe política de inversiones?
@@ -755,10 +755,10 @@
     <t>Gestión integrada con mercado, cash forecast, riesgos, accounting, compliance y decisiones de reinversión/desinversión.</t>
   </si>
   <si>
-    <t>AI analiza rendimiento y riesgo, detecta concentración o desviaciones y recomienda rebalanceo o reinversión según escenarios.</t>
-  </si>
-  <si>
-    <t>Generate investing strategies; Enhance cash flow analysis; AI agents for algorithmic trading and market simulation</t>
+    <t>IA analiza rendimiento y riesgo, detecta concentración o desviaciones y recomienda rebalanceo o reinversión según escenarios.</t>
+  </si>
+  <si>
+    <t>Generación de estrategias de inversión; Mejora del análisis de flujo de caja; Agentes de IA para trading algorítmico y simulación de mercado</t>
   </si>
   <si>
     <t>¿Se monitoriza rentabilidad y riesgo de la cartera?
@@ -791,10 +791,10 @@
     <t>Integración completa con planificación financiera, estructura de capital, riesgos, escenarios, inversiones operativas y capital allocation.</t>
   </si>
   <si>
-    <t>AI simula liquidez futura, necesidades de financiación y oportunidades de inversión, recomendando asignación óptima de excedentes.</t>
-  </si>
-  <si>
-    <t>Predictive cash flow forecasting tool; Generate investing strategies; Identify past data patterns to predict and improve future financial performance</t>
+    <t>IA simula liquidez futura, necesidades de financiación y oportunidades de inversión, recomendando asignación óptima de excedentes.</t>
+  </si>
+  <si>
+    <t>Herramienta predictiva de previsión de flujo de caja; Generación de estrategias de inversión; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
   </si>
   <si>
     <t>¿Las inversiones se conectan con cash forecast?
@@ -827,10 +827,10 @@
     <t>Control integrado con workflows, alertas de límites, evidencias, accounting, compliance y revisión de performance.</t>
   </si>
   <si>
-    <t>AI genera reporting ejecutivo, detecta incumplimientos potenciales, explica variaciones y recomienda acciones correctivas.</t>
-  </si>
-  <si>
-    <t>Generate executive level overview of company financial health; FinanceAI Insights Platform; Predictive compliance monitoring</t>
+    <t>IA genera reporting ejecutivo, detecta incumplimientos potenciales, explica variaciones y recomienda acciones correctivas.</t>
+  </si>
+  <si>
+    <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Monitorización predictiva del cumplimiento</t>
   </si>
   <si>
     <t>¿Se reporta cumplimiento de política?

--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="320">
   <si>
     <t>Capacidad</t>
   </si>
@@ -1018,6 +1018,66 @@
   </si>
   <si>
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas, validar resultados con responsables de Tesorería y preservar la conexión entre liquidez, riesgos, financiación e inversiones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de informes fiscales; Detección de inconsistencias en datos maestros; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de provisiones omitidas; Análisis de desviaciones con explicación automática; Conciliación a nivel de transacción</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detección de inconsistencias en datos maestros; Flujos guiados de cambio en datos maestros; Generación de documentación de metadatos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Análisis de desviaciones con explicación automática; Analista digital de Finanzas bajo demanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimización de operaciones de divisa; Agentes de IA para análisis de riesgo crediticio; Monitorización predictiva del cumplimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimización de operaciones de divisa; Generación de estrategias de inversión</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentes de IA para análisis de riesgo crediticio; Valoración predictiva de la compañía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión predictiva de flujo de caja; Optimización de operaciones de divisa; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de estrategias de inversión; Valoración predictiva de la compañía; Visión ejecutiva de la salud financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Previsión predictiva de flujo de caja; Informes de investigación y KYC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agentes de IA para trading y simulación de mercado; Generación de estrategias de inversión; Valoración predictiva de la compañía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inteligencia de mercado; Generación de estrategias de inversión; Agentes de IA para trading y simulación de mercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión predictiva de flujo de caja; Análisis de caja y riesgo de liquidez; Optimización de la liquidez intradía</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimización de la liquidez intradía; Análisis de caja y riesgo de liquidez; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condiciones de pago óptimas para el DSO; Momento óptimo de pago a proveedores; Gestión dinámica de inventario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda; Análisis de desviaciones con explicación automática</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Análisis de caja y riesgo de liquidez; Generación de estrategias de inversión; Previsión predictiva de flujo de caja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de estrategias de inversión; Análisis de caja y riesgo de liquidez; Agentes de IA para trading y simulación de mercado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Previsión predictiva de flujo de caja; Generación de estrategias de inversión; Patrones históricos para predecir el rendimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visión ejecutiva de la salud financiera; Analista digital de Finanzas bajo demanda; Monitorización predictiva del cumplimiento</t>
   </si>
 </sst>
 </file>
@@ -1772,7 +1832,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1830,7 +1890,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>301</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1888,7 +1948,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1946,7 +2006,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -2004,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>304</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -2062,7 +2122,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -2120,7 +2180,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -2178,7 +2238,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -2236,7 +2296,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>308</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2294,7 +2354,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>309</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2352,7 +2412,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2410,7 +2470,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2468,7 +2528,7 @@
         <v>162</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2526,7 +2586,7 @@
         <v>173</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -2584,7 +2644,7 @@
         <v>184</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -2642,7 +2702,7 @@
         <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>196</v>
+        <v>315</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -2700,7 +2760,7 @@
         <v>207</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -2758,7 +2818,7 @@
         <v>218</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -2816,7 +2876,7 @@
         <v>229</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -2874,7 +2934,7 @@
         <v>240</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -3932,7 +3992,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G21" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -3963,7 +4023,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>301</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3994,7 +4054,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4025,7 +4085,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4056,7 +4116,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>304</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4087,7 +4147,7 @@
         <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4118,7 +4178,7 @@
         <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4149,7 +4209,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4180,7 +4240,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>308</v>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4211,7 +4271,7 @@
         <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>309</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4242,7 +4302,7 @@
         <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4273,7 +4333,7 @@
         <v>154</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4304,7 +4364,7 @@
         <v>166</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="G14" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4335,7 +4395,7 @@
         <v>177</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="G15" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4366,7 +4426,7 @@
         <v>188</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="G16" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4397,7 +4457,7 @@
         <v>199</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>196</v>
+        <v>315</v>
       </c>
       <c r="G17" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4428,7 +4488,7 @@
         <v>211</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="G18" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4459,7 +4519,7 @@
         <v>222</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="G19" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4490,7 +4550,7 @@
         <v>233</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="G20" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4521,7 +4581,7 @@
         <v>244</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="G21" s="2" t="str">
         <f t="shared" si="0"/>
@@ -4581,7 +4641,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>300</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -4598,7 +4658,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>301</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -4615,7 +4675,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>302</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -4632,7 +4692,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -4649,7 +4709,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>304</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -4666,7 +4726,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>305</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -4683,7 +4743,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -4700,7 +4760,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -4717,7 +4777,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>308</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -4734,7 +4794,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>309</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -4751,7 +4811,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>310</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -4768,7 +4828,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>311</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>
@@ -4785,7 +4845,7 @@
         <v>156</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>163</v>
+        <v>312</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>162</v>
@@ -4802,7 +4862,7 @@
         <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>174</v>
+        <v>313</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>173</v>
@@ -4819,7 +4879,7 @@
         <v>178</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>184</v>
@@ -4836,7 +4896,7 @@
         <v>189</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>196</v>
+        <v>315</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>195</v>
@@ -4853,7 +4913,7 @@
         <v>201</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>208</v>
+        <v>316</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>207</v>
@@ -4870,7 +4930,7 @@
         <v>212</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>219</v>
+        <v>317</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>218</v>
@@ -4887,7 +4947,7 @@
         <v>223</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>230</v>
+        <v>318</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>229</v>
@@ -4904,7 +4964,7 @@
         <v>234</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>241</v>
+        <v>319</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>240</v>

--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -203,7 +203,7 @@
     <t>Gobierno integrado con bancos, ERP, TMS, pagos, deuda y reporting, con controles automáticos y gestión de incidencias.</t>
   </si>
   <si>
-    <t>IA detecta inconsistencias en datos maestros, propone remediación y guía workflows adaptativos de cambios financieros/bancarios.</t>
+    <t>IA detecta inconsistencias en datos maestros, propone remediación y guía flujos de trabajo adaptativos de cambios financieros/bancarios.</t>
   </si>
   <si>
     <t>Identificación de inconsistencias en los registros de datos maestros; Flujos guiados y adaptables para cambios en datos maestros; Generación de documentación de metadatos</t>
@@ -239,7 +239,7 @@
     <t>Reporting integrado con deuda, liquidez, inversiones, riesgos financieros, forecast y acciones de gestión.</t>
   </si>
   <si>
-    <t>Reporting basado en IA con narrativa automática, explicación de drivers, alertas tempranas y recomendaciones sobre coste financiero y liquidez.</t>
+    <t>Informes basados en IA, con narrativa automática, explicación de los drivers, alertas tempranas y recomendaciones sobre coste financiero y liquidez.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes; FinanceAI Insights Platform</t>
@@ -314,7 +314,7 @@
     <t>Gestión integrada de FX con forecast, operaciones, posiciones, escenarios, límites, efectividad de cobertura y contabilidad.</t>
   </si>
   <si>
-    <t>IA identifica patrones FX, anticipa exposición, simula escenarios y recomienda estrategias de cobertura según riesgo, coste y política.</t>
+    <t>IA identifica patrones de tipo de cambio, anticipa exposición, simula escenarios y recomienda estrategias de cobertura según riesgo, coste y política.</t>
   </si>
   <si>
     <t>Optimización de las operaciones de divisa evaluando datos de tipo de cambio e identificando patrones y tendencias para reducir riesgos financieros; Análisis predictivo + GenAI; Generación de estrategias de inversión</t>
@@ -386,7 +386,7 @@
     <t>Stress testing integrado con cash forecast, deuda, covenants, FX, tipos, liquidez, capital allocation y comités.</t>
   </si>
   <si>
-    <t>IA simula escenarios dinámicos, identifica early warnings, estima impactos y recomienda respuestas financieras preventivas.</t>
+    <t>IA simula escenarios dinámicos, identifica alertas tempranas, estima impactos y recomienda respuestas financieras preventivas.</t>
   </si>
   <si>
     <t>Herramienta predictiva de previsión de flujo de caja; Optimización de las operaciones de divisa; Identificación de patrones históricos para predecir y mejorar el rendimiento financiero futuro</t>
@@ -497,7 +497,7 @@
     <t>Ejecución integrada con estrategia de financiación, ventanas de mercado, rating, inversores, bancos, riesgos y reporting de operación.</t>
   </si>
   <si>
-    <t>IA analiza condiciones de mercado, simula alternativas de instrumentos y recomienda timing, estructura y fuentes óptimas de financiación.</t>
+    <t>IA analiza condiciones de mercado, simula alternativas de instrumentos y recomienda momento, estructura y fuentes óptimas de financiación.</t>
   </si>
   <si>
     <t>Agentes de IA para trading algorítmico y simulación de mercado; Generación de estrategias de inversión; Valoración predictiva de la compañía a partir del análisis de datos financieros</t>
@@ -533,7 +533,7 @@
     <t>Inteligencia integrada con estrategia de financiación, deuda, inversión, riesgos, escenarios y decisiones de timing.</t>
   </si>
   <si>
-    <t>IA sintetiza señales de mercado, detecta oportunidades de financiación, genera alertas y recomienda acciones de capital markets.</t>
+    <t>IA sintetiza señales de mercado, detecta oportunidades de financiación, genera alertas y recomienda acciones de mercados de capitales.</t>
   </si>
   <si>
     <t>Inteligencia de mercado de nueva generación; Generación de estrategias de inversión; Agentes de IA para trading algorítmico y simulación de mercado</t>
@@ -572,7 +572,7 @@
     <t>Forecast integrado con ERP/TMS, presupuesto, ventas, compras, deuda, working capital, escenarios y revisión de desviaciones.</t>
   </si>
   <si>
-    <t>Cash forecasting predictivo basado en IA con aprendizaje histórico, señales operativas, escenarios dinámicos y recomendaciones de acción.</t>
+    <t>Previsión de caja predictiva basada en IA, con aprendizaje sobre el histórico, señales operativas, escenarios dinámicos y recomendación de acciones.</t>
   </si>
   <si>
     <t>Herramienta predictiva de previsión de flujo de caja; Mejora del análisis de flujo de caja, minimizando riesgos de liquidez, mejorando la precisión de las previsiones y maximizando el rendimiento de la tesorería; Optimización de la liquidez intradía</t>
@@ -644,7 +644,7 @@
     <t>Gestión integrada de liquidez con O2C/P2P, forecast, deuda, inversiones, pagos, cobros, DSO/DPO/DIO y escenarios.</t>
   </si>
   <si>
-    <t>IA recomienda términos de pago/cobro, timing óptimo, acciones sobre working capital e inversiones de excedentes según liquidez y riesgo.</t>
+    <t>IA recomienda términos de pago/cobro, momento óptimo, acciones sobre capital circulante e inversiones de excedentes según liquidez y riesgo.</t>
   </si>
   <si>
     <t>Recomendación de condiciones de pago óptimas para mejorar el DSO; Recomendación del momento óptimo de pago; Gestión dinámica de inventario</t>
@@ -680,7 +680,7 @@
     <t>Rutinas integradas de liquidez con comité, decisiones, seguimiento de acciones, alertas, escenarios y beneficios esperados.</t>
   </si>
   <si>
-    <t>Reporting basado en IA con narrativa ejecutiva, alertas, explicación de desviaciones, escenarios y recomendaciones de liquidez.</t>
+    <t>Informes basados en IA, con narrativa ejecutiva, alertas, explicación de las desviaciones, escenarios y recomendaciones de liquidez.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
@@ -827,7 +827,7 @@
     <t>Control integrado con workflows, alertas de límites, evidencias, accounting, compliance y revisión de performance.</t>
   </si>
   <si>
-    <t>IA genera reporting ejecutivo, detecta incumplimientos potenciales, explica variaciones y recomienda acciones correctivas.</t>
+    <t>IA genera los informes ejecutivos, detecta incumplimientos potenciales, explica las variaciones y recomienda acciones correctivas.</t>
   </si>
   <si>
     <t>Generación de una visión ejecutiva de la salud financiera de la compañía; FinanceAI Insights Platform; Monitorización predictiva del cumplimiento</t>

--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -110,7 +110,7 @@
     <t>Comentarios / hallazgos</t>
   </si>
   <si>
-    <t>Contabilidad y provisión fiscal</t>
+    <t>Control y tratamiento contable</t>
   </si>
   <si>
     <t>1.1 Gobierno contable-fiscal de operaciones de tesorería</t>
@@ -995,7 +995,7 @@
     <t>Dominio</t>
   </si>
   <si>
-    <t>Tesorería: Contabilidad y provisión fiscal, Gestión de riesgos financieros, Mercados de deuda y capitales, Gestión de cash flow y reporte e Inversiones.</t>
+    <t>Tesorería: Control y tratamiento contable, Gestión de riesgos financieros, Mercados de deuda y capitales, Gestión de cash flow y reporte e Inversiones.</t>
   </si>
   <si>
     <t>Escala F3M</t>
@@ -1261,7 +1261,7 @@
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>Contabilidad y provisión fiscal</c:v>
+                  <c:v>Control y tratamiento contable</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Gestión de riesgos financieros</c:v>

--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -113,40 +113,40 @@
     <t>Control y tratamiento contable</t>
   </si>
   <si>
-    <t>1.1 Gobierno contable-fiscal de operaciones de tesorería</t>
-  </si>
-  <si>
-    <t>Evaluar si las operaciones de tesorería tienen un tratamiento contable-fiscal gobernado, trazable y coordinado con cierre, fiscalidad y reporting.</t>
-  </si>
-  <si>
-    <t>Registro contable-fiscal de operaciones de tesorería manual, reactivo y con baja trazabilidad de criterios y aprobaciones.</t>
-  </si>
-  <si>
-    <t>Criterios básicos definidos para operaciones relevantes, aunque con revisiones manuales y variabilidad entre entidades.</t>
-  </si>
-  <si>
-    <t>Políticas documentadas para tratamiento contable-fiscal de instrumentos, intereses, retenciones, comisiones y ajustes de tesorería.</t>
-  </si>
-  <si>
-    <t>Proceso integrado con cierre, fiscalidad, reporting y controles automáticos, con revisión periódica de criterios y excepciones.</t>
-  </si>
-  <si>
-    <t>Modelo basado en IA que detecta tratamientos anómalos, sugiere clasificaciones contable-fiscales y explica variaciones de resultados financieros.</t>
+    <t>1.1 Gobierno del tratamiento contable de operaciones de tesorería</t>
+  </si>
+  <si>
+    <t>Evaluar si las operaciones de tesorería tienen un tratamiento contable gobernado, trazable y coordinado con cierre contable y reporting.</t>
+  </si>
+  <si>
+    <t>Registro contable de operaciones de tesorería manual, reactivo y con baja trazabilidad de criterios y aprobaciones.</t>
+  </si>
+  <si>
+    <t>Criterios contables básicos definidos para operaciones relevantes, aunque con revisiones manuales y variabilidad entre entidades.</t>
+  </si>
+  <si>
+    <t>Políticas documentadas para tratamiento contable de instrumentos, intereses, comisiones y ajustes de tesorería.</t>
+  </si>
+  <si>
+    <t>Proceso integrado con cierre contable, reporting y controles automáticos, con revisión periódica de criterios y excepciones.</t>
+  </si>
+  <si>
+    <t>Modelo basado en IA que detecta tratamientos anómalos, sugiere clasificaciones contables y explica variaciones de resultados financieros.</t>
   </si>
   <si>
     <t>Generación precisa de informes fiscales; Identificación de inconsistencias en los registros de datos maestros; Generación de análisis de desviaciones de cuentas con explicaciones inteligentes</t>
   </si>
   <si>
-    <t>¿Existen políticas contable-fiscales para operaciones de tesorería?
-¿Se revisan tratamientos de intereses, retenciones y comisiones?
+    <t xml:space="preserve">¿Existen políticas contables para operaciones de tesorería?
+¿Se revisa el tratamiento contable de instrumentos, intereses y comisiones?
 ¿Se conectan con cierre y reporting?
 ¿Hay trazabilidad de ajustes?</t>
   </si>
   <si>
-    <t>Políticas contables/fiscales; registros de operaciones; conciliaciones; evidencias de revisión; workpapers; reporting financiero.</t>
-  </si>
-  <si>
-    <t>Definir gobierno contable-fiscal de tesorería con políticas, controles, trazabilidad, owners y revisión recurrente de excepciones.</t>
+    <t>Políticas contables; registros de operaciones; conciliaciones; evidencias de revisión; workpapers; reporting financiero.</t>
+  </si>
+  <si>
+    <t>Definir gobierno del tratamiento contable de tesorería con políticas, controles, trazabilidad, owners y revisión recurrente de excepciones.</t>
   </si>
   <si>
     <t>1.2 Registro, conciliación y devengo de intereses y comisiones</t>
@@ -1020,7 +1020,7 @@
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas, validar resultados con responsables de Tesorería y preservar la conexión entre liquidez, riesgos, financiación e inversiones.</t>
   </si>
   <si>
-    <t xml:space="preserve">Generación de informes fiscales; Detección de inconsistencias en datos maestros; Análisis de desviaciones con explicación automática</t>
+    <t xml:space="preserve">Detección de asientos inusuales en el cierre; Detección de inconsistencias en datos maestros; Análisis de desviaciones con explicación automática</t>
   </si>
   <si>
     <t xml:space="preserve">Detección de provisiones omitidas; Análisis de desviaciones con explicación automática; Conciliación a nivel de transacción</t>

--- a/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
+++ b/F3M_Tesoreria_assessment_ready_AI_v0.xlsx
@@ -146,7 +146,7 @@
     <t>Políticas contables; registros de operaciones; conciliaciones; evidencias de revisión; workpapers; reporting financiero.</t>
   </si>
   <si>
-    <t>Definir gobierno del tratamiento contable de tesorería con políticas, controles, trazabilidad, owners y revisión recurrente de excepciones.</t>
+    <t>Definir gobierno del tratamiento contable de tesorería con políticas, controles, trazabilidad, responsables y revisión recurrente de excepciones.</t>
   </si>
   <si>
     <t>1.2 Registro, conciliación y devengo de intereses y comisiones</t>
@@ -218,7 +218,7 @@
     <t>Maestros bancarios; workflows de alta/cambio; logs; controles de calidad; incidencias; aprobaciones; políticas de datos.</t>
   </si>
   <si>
-    <t>Implantar gobierno de master data financiero/bancario con owners, workflow, controles automáticos, trazabilidad y gestión de incidencias.</t>
+    <t>Implantar gobierno de datos maestros financieros y bancarios con responsables, flujo de trabajo, controles automáticos, trazabilidad y gestión de incidencias.</t>
   </si>
   <si>
     <t>1.4 Reporting financiero de resultados de tesorería</t>
@@ -254,7 +254,7 @@
     <t>Reporting de tesorería; análisis de variaciones; KPIs de coste financiero; comité financiero; forecast; acciones de gestión.</t>
   </si>
   <si>
-    <t>Crear reporting financiero de tesorería con drivers, KPIs, narrativa ejecutiva, conexión con forecast y recomendaciones de acción.</t>
+    <t>Crear informes financieros de tesorería con drivers, KPIs, narrativa ejecutiva, conexión con la previsión y recomendaciones de acción.</t>
   </si>
   <si>
     <t>Gestión de riesgos financieros</t>
@@ -293,7 +293,7 @@
     <t>Política de riesgos; límites; exposiciones; reportes de comité; aprobaciones; métricas VaR/sensibilidad; excepciones.</t>
   </si>
   <si>
-    <t>Definir marco integral de riesgos financieros con políticas, límites, métricas, reporting, governance y workflow de excepciones.</t>
+    <t>Definir marco integral de riesgos financieros con políticas, límites, métricas, informes, gobierno y flujo de excepciones.</t>
   </si>
   <si>
     <t>2.2 Medición y cobertura de riesgo de divisa</t>
@@ -329,7 +329,7 @@
     <t>Mapa de exposición FX; forecast por moneda; contratos de cobertura; sensibilidad; hedge effectiveness; reporting de límites.</t>
   </si>
   <si>
-    <t>Implantar modelo de gestión FX con forecast de exposición, límites, escenarios, tracking de coberturas y recomendaciones de mitigación.</t>
+    <t>Implantar modelo de gestión del riesgo de divisa con previsión de exposición, límites, escenarios, seguimiento de coberturas y recomendaciones de mitigación.</t>
   </si>
   <si>
     <t>2.3 Gestión de riesgo de tipos, contraparte y crédito financiero</t>
@@ -401,7 +401,7 @@
     <t>Modelos de escenarios; supuestos macro; sensibilidad; reportes de stress; actas de comité; decisiones preventivas.</t>
   </si>
   <si>
-    <t>Crear framework de stress testing financiero con variables clave, impactos, alertas y planes de respuesta.</t>
+    <t>Crear marco de pruebas de estrés financieras con variables clave, impactos, alertas y planes de respuesta.</t>
   </si>
   <si>
     <t>Mercados de deuda y capitales</t>
@@ -476,7 +476,7 @@
     <t>Contratos de deuda; covenant tracker; calendario de vencimientos; reportes a bancos; actas; forecasts; documentación financiera.</t>
   </si>
   <si>
-    <t>Implantar gestión integrada de deuda con covenant tracking, alertas, forecast, repositorio documental y estrategia de relación bancaria.</t>
+    <t>Implantar gestión integrada de deuda con seguimiento de covenants, alertas, previsión, repositorio documental y estrategia de relación bancaria.</t>
   </si>
   <si>
     <t>3.3 Acceso a mercados, instrumentos y ejecución de operaciones</t>
@@ -512,7 +512,7 @@
     <t>Análisis de alternativas; term sheets; comparativas de coste; aprobaciones; rating; investor/bank materials; documentación de operación.</t>
   </si>
   <si>
-    <t>Crear metodología de evaluación y ejecución de instrumentos financieros con escenarios de mercado, coste/riesgo, approvals y lessons learned.</t>
+    <t>Crear metodología de evaluación y ejecución de instrumentos financieros con escenarios de mercado, coste y riesgo, aprobaciones y lecciones aprendidas.</t>
   </si>
   <si>
     <t>3.4 Reporting de capital markets e inteligencia de financiación</t>
@@ -548,7 +548,7 @@
     <t>Reportes de mercado; benchmarks; curvas de tipos; spreads; actas de comité; recomendaciones de financiación; alertas.</t>
   </si>
   <si>
-    <t>Implantar capital markets intelligence con fuentes, indicadores, alertas, benchmarks y conexión con estrategia de financiación.</t>
+    <t>Implantar inteligencia de mercados de capitales con fuentes, indicadores, alertas, referencias de mercado y conexión con la estrategia de financiación.</t>
   </si>
   <si>
     <t>Gestión de cash flow y reporte</t>
@@ -587,7 +587,7 @@
     <t>Modelo de forecast; calendario; inputs; histórico de precisión; desviaciones; TMS/ERP; comités de liquidez.</t>
   </si>
   <si>
-    <t>Implantar modelo de cash forecasting con metodología, owners, integración de fuentes, medición de precisión y escenarios.</t>
+    <t>Implantar modelo de previsión de tesorería con metodología, responsables, integración de fuentes, medición de precisión y escenarios.</t>
   </si>
   <si>
     <t>4.2 Posición de liquidez y visibilidad bancaria</t>
@@ -623,7 +623,7 @@
     <t>Reportes de posición; extractos bancarios; TMS; cash pooling; saldos por divisa; restricciones; alertas; conciliaciones.</t>
   </si>
   <si>
-    <t>Implantar visibilidad integrada de liquidez con conexiones bancarias, cash pooling, alertas y análisis de saldos disponibles/restringidos.</t>
+    <t>Implantar visibilidad integrada de liquidez con conexiones bancarias, centralización de tesorería, alertas y análisis de saldos disponibles y restringidos.</t>
   </si>
   <si>
     <t>4.3 Gestión de liquidez, working capital y decisiones de caja</t>
@@ -659,7 +659,7 @@
     <t>KPIs working capital; aging; pagos; cobros; inventario; cash forecast; acciones de mejora; comités de cash.</t>
   </si>
   <si>
-    <t>Crear modelo de optimización de liquidez y working capital con KPIs, escenarios, acciones y recomendaciones de cobro/pago/inventario.</t>
+    <t>Crear modelo de optimización de liquidez y capital circulante con KPIs, escenarios, acciones y recomendaciones de cobro, pago e inventario.</t>
   </si>
   <si>
     <t>4.4 Reporting de tesorería y rutinas de gestión de liquidez</t>
@@ -695,7 +695,7 @@
     <t>Pack de tesorería; actas de comité; KPIs; forecast; tracker de acciones; escenarios; reportes de desviación.</t>
   </si>
   <si>
-    <t>Formalizar reporting y rutinas de liquidez con pack estándar, decisiones, actions tracker, escenarios y recomendaciones ejecutivas.</t>
+    <t>Formalizar informes y rutinas de liquidez con un paquete estándar, decisiones, seguimiento de acciones, escenarios y recomendaciones ejecutivas.</t>
   </si>
   <si>
     <t>Inversiones</t>
@@ -734,7 +734,7 @@
     <t>Política de inversiones; cartera; límites; aprobaciones; reportes de rentabilidad; cash forecast; rating contrapartes.</t>
   </si>
   <si>
-    <t>Definir política y gobierno de inversiones de excedentes con límites, instrumentos, contrapartes, liquidez, reporting y revisión periódica.</t>
+    <t>Definir política y gobierno de inversiones de excedentes con límites, instrumentos, contrapartes, liquidez, informes y revisión periódica.</t>
   </si>
   <si>
     <t>5.2 Gestión de cartera, rentabilidad y riesgo de inversiones</t>
@@ -806,7 +806,7 @@
     <t>Cash forecast; plan financiero; cartera de inversiones; vencimientos; escenarios; decisiones de inversión/desinversión; comités.</t>
   </si>
   <si>
-    <t>Diseñar proceso integrado de inversiones y liquidez con escenarios, restricciones, vencimientos, necesidades futuras y capital allocation.</t>
+    <t>Diseñar proceso integrado de inversiones y liquidez con escenarios, restricciones, vencimientos, necesidades futuras y asignación de capital.</t>
   </si>
   <si>
     <t>5.4 Reporting, cumplimiento y control de inversiones</t>
@@ -842,7 +842,7 @@
     <t>Reporting de inversiones; policy compliance; excepciones; aprobaciones; logs; actas de comité; análisis de rendimiento/riesgo.</t>
   </si>
   <si>
-    <t>Crear reporting y control de inversiones con límites, evidencias, alertas, performance, compliance y decisiones trazables.</t>
+    <t>Crear informes y control de inversiones con límites, evidencias, alertas, rentabilidad, cumplimiento y decisiones trazables.</t>
   </si>
   <si>
     <t>Score global dominio</t>
